--- a/data/trans_dic/IP31C_R_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31C_R_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1,77; 14,87</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,55; 13,22</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,29</t>
+          <t>0,91; 7,23</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 7,0</t>
+          <t>6,24; 14,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,47; 12,17</t>
+          <t>1,92; 7,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 8,51</t>
+          <t>4,61; 9,35</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,02; 16,41</t>
+          <t>4,71; 12,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 10,09</t>
+          <t>8,86; 18,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,66; 11,95</t>
+          <t>7,48; 13,27</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 11,88</t>
+          <t>10,48; 18,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,74; 14,94</t>
+          <t>8,8; 17,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 12,32</t>
+          <t>10,41; 15,92</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 9,38</t>
+          <t>8,8; 13,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,02; 10,84</t>
+          <t>7,49; 11,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,89; 9,62</t>
+          <t>8,71; 11,83</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2198</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2464</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2198</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>647; 5436</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>683; 5840</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>676; 5624</t>
+          <t>709; 5648</t>
         </is>
       </c>
     </row>
@@ -957,17 +957,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>14866</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20616</t>
+          <t>20794</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2740; 11081</t>
+          <t>9803; 22749</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9951; 22138</t>
+          <t>2776; 11145</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13907; 28968</t>
+          <t>13922; 28216</t>
         </is>
       </c>
     </row>
@@ -1030,17 +1030,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20433</t>
+          <t>15679</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>22889</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34356</t>
+          <t>38568</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13884; 28393</t>
+          <t>9422; 24433</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8336; 21433</t>
+          <t>15472; 31810</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25663; 46061</t>
+          <t>28020; 49725</t>
         </is>
       </c>
     </row>
@@ -1103,17 +1103,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>83</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>21697</t>
+          <t>40573</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>34170</t>
+          <t>30711</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55867</t>
+          <t>71284</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13868; 32570</t>
+          <t>30527; 53470</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23552; 45451</t>
+          <t>22459; 44083</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42571; 71281</t>
+          <t>56891; 87045</t>
         </is>
       </c>
     </row>
@@ -1176,17 +1176,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>167</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>48040</t>
+          <t>73317</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>65264</t>
+          <t>59528</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113304</t>
+          <t>132844</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36228; 61083</t>
+          <t>60289; 90234</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>52179; 80544</t>
+          <t>46171; 73643</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96021; 134031</t>
+          <t>113299; 153988</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31C_R_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31C_R_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que realizan algún voluntariado (tasa de respuesta: 99,62%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1,77; 14,87</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,91; 7,23</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>9,47%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4,1%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>6,24; 14,49</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1,92; 7,7</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4,61; 9,35</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10,29%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>4,71; 12,21</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>8,86; 18,21</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>7,48; 13,27</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>13,93%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12,03%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>10,48; 18,35</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8,8; 17,26</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>10,41; 15,92</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>10,7%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>9,66%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>10,21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>8,8; 13,17</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>7,49; 11,95</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8,71; 11,83</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,47 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.06015753221886921</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.02814544153348261</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2198</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2198</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.01769976418123858</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="n">
+        <v>0.009074529757249468</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>647; 5436</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>709; 5648</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.148743892896998</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="n">
+        <v>0.07230768898797718</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +603,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.09466367744687629</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.04095588229359183</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.06890470903598508</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>14866</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5928</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>20794</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.0624234058875789</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.01917740146614758</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.04613326105605183</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>9803; 22749</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2776; 11145</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>13922; 28216</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1448612236749762</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.07700172703633004</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.09349871068771934</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +658,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.07834438314153229</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.131038961621694</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.102902356865743</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>15679</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>22889</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>38568</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.04708178637901828</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.08857954022037486</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.07476025208946638</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>9422; 24433</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>15472; 31810</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>28020; 49725</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1220890422592899</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.1821120829119761</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.132671428624054</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +713,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1392551264213534</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1202769747104885</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1303912809226732</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>40573</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>30711</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>71284</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.1047759976929249</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.08796018389410074</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.1040638961930189</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>30527; 53470</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>22459; 44083</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>56891; 87045</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.1835191976711239</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.1726474114434883</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.159219411626495</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +768,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.1070202744247137</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.09658715430753964</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1020793328945715</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>73317</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>59528</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>132844</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.08800393469622064</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.07491494069715941</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.08706008836467097</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>60289; 90234</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>46171; 73643</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>113299; 153988</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.1317150284086639</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.1194896195260067</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.118326203526282</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +833,445 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que realizan algún voluntariado (tasa de respuesta: 99,62%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>2198</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>647</v>
+      </c>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="n">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>5436</v>
+      </c>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="n">
+        <v>5648</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>14866</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>5928</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>20794</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>9803</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>2776</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>13922</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>22749</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>11145</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>28216</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>15679</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>22889</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>38568</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>9422</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>15472</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>28020</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>24433</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>31810</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>49725</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>40573</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>30711</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>71284</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>30527</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>22459</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>56891</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>53470</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>44083</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>87045</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>73317</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>59528</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>132844</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>60289</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>46171</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>113299</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>90234</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>73643</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>153988</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>